--- a/important_mails_2026-03-22.xlsx
+++ b/important_mails_2026-03-22.xlsx
@@ -1142,7 +1142,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1157,167 +1157,21 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
+          <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
+          <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Hola, Weihai EU:
- Para cumplir nuestros requisitos de registro del impuesto sobre el valor añadido (IVA) europeo, necesitamos que nos proporciones más información.
- ¿A qué se debe esto?
- De acuerdo con nuestros requisitos de registro a efectos fiscales en Europa, tienes que proporcionarnos un número de identificación fiscal válido de todos los países en los que consideremos que tienes obligación de registrarte a efectos fiscales o confirmar el estado de registro en la Ventanilla Única del IVA (OSS) en tu país de origen.
- Hemos detectado que tu cuenta tiene que cumplir una serie de requisitos para el registro a efectos fiscales en la Unión Europea, el Reino Unido, Noruega y Suiza, donde tienes la obligación de registrarte a efectos fiscales. En concreto, es posible que tengas que tomar medidas para lo siguiente:
- Polonia
- Para más información, consulta Información sobre el impuesto sobre el valor añadido (IVA) europeo .
- ¿Cómo evito la desactivación de mi cuenta?
- Para evitar la desactivación de la cuenta, consulta la sección "Acciones prioritarias" de la página Estado de la cuenta en los próximos 45 días. Desde ahí podrás hacer lo siguiente:
-- Revisar la información que tienes </t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>96
- Dzień dobry Weihai EU,
- potrzebujemy od Ciebie dodatkowych informacji, które pozwolą Ci spełnić europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT.
- Dlaczego tak się stało?
- Zgodnie z europejskimi wymaganiami Amazon dotyczącymi rejestracji jako podatnik VAT musisz podać nam ważny numer VAT dla wszystkich krajów, w których według nas podlegasz obowiązkowi rejestracji jako podatnik VAT, lub potwierdzenie statusu rejestracji w procedurze unijnej w Twoim kraju macierzystym.
- Ustaliliśmy, że w przypadku Twojego konta w Unii Europejskiej, Zjednoczonym Królestwie, Norwegii i Szwajcarii, gdzie masz zobowiązania z tytułu VAT, istnieją wymogi w zakresie rejestracji jako podatnik VAT. Podjęcie działań może być w szczególności wymagane w następujących przypadkach:
- Polska
- Więcej informacji znajdziesz na stronie Informacje dotyczące podatku VAT w Europie .
- Jak mogę zapobiec dezaktywacji konta?
- Aby uniknąć dezaktywacji konta, w ciągu najbliższych 45 dni odwiedź sekcję „Działania priorytetowe” na stronie Kondycja konta . W sekcji tej można:
-- zweryfikować istniejące informacje dotyczące wymienionych krajów
-- przesłać informacje o VAT za pośrednictwem portali „Informacje o</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
- la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96
- Gentile Weihai EU,
- Ai fini della conformità ai requisiti di registrazione IVA in Europa di Amazon, ti chiediamo di fornirci ulteriori informazioni.
- Ciò a cosa è dovuto?
- In base ai requisiti di registrazione IVA in Europa di Amazon, sei tenuto a fornirci un numero di partita IVA valido per tutti i paesi in cui riteniamo che tu abbia l'obbligo di effettuare tale registrazione o una conferma dello stato Union One-Stop Shop (OSS) relativo al tuo paese di registrazione.
- Vi sono dei requisiti per la registrazione ai fini IVA che il tuo account deve soddisfare nei paesi in cui sei soggetto a obblighi in materia di IVA (stati dell'Unione europea, Regno Unito, Norvegia e Svizzera). Nello specifico, potrebbe essere necessario un intervento da parte tua per quanto segue:
- Polonia
- Per maggiori informazioni, consulta la pagina di aiuto Informazioni sull'IVA in Europa .
- Come faccio a evitare la disattivazione dell'account?
- Per evitare la disattivazione dell'account, visita entro i prossimi 45 giorni la sezione relativa alle azioni prioritarie della pagina Stato dell'account . Da qui, potrai effettuare le seguenti operazioni:
-- Verificare le informazioni esistenti per i paesi in elenco</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-04-02</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1338,39 +1192,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1394,39 +1248,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1449,143 +1303,40 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>[Action Required] Provide additional information within 45 days to
- avoid account deactivation under European VAT registration requirements</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai EU,
- We need you to provide additional information in order to comply with Amazon’s European Value Added Tax (VAT) registration requirements.
- Why is this happening?
- According to Amazon’s European VAT registration requirements you must provide us with a valid VAT Registration Number (‘VRN’) for all the countries in which we believe you have a VAT registration obligation or confirmation of the Union One-Stop Shop (OSS) status for your home country.
- We identified VAT registration requirements for your account in the European Union, the United Kingdom, Norway, and Switzerland in which you have VAT obligation. Specifically, action may be required for the following:
- Poland
- To learn more, go to the European Value Added Tax Information Help page.
- How do I avoid account deactivation?
- To avoid account deactivation, within the next 45 days visit the Priority Actions section on your Account Health page . From there, you will be able to:
-- Verify your existing information for listed countries
-- Submit VAT information through Business Information and Tax Setting portals
-- Submit required documentation for extension or exemption requests
- What happens if I don’t provide th</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>[Action required] Provide additional information within 45 days to
- avoid account deactivation under European VAT registration requirements</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai EU,
- We need you to provide additional information in order to comply with Amazon’s European Value Added Tax (VAT) registration requirements.
- Why is this happening?
- According to Amazon’s European VAT registration requirements, you must provide us with a valid VAT registration number (“VRN”) for all the countries in which we believe you have a VAT registration obligation, or confirmation of the Union One-Stop Shop (OSS) status for your home country.
- We identified VAT registration requirements for your account in the European Union, the United Kingdom, Norway and Switzerland in which you have Value Added Tax (VAT) obligation. Specifically, action may be required for the following:
- Poland
- To learn more, go to the European Value Added Tax information help page.
- How do I avoid account deactivation?
- To avoid account deactivation, within the next 45 days visit the Priority actions section on your Account Health page . From there, you will be able to:
-- Verify your existing information for listed countries
-- Submit Value Added Tax (VAT) information through business information and tax setting portals
-- Submit required documentation for extension or exemption request</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -1601,39 +1352,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1653,39 +1404,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -1699,39 +1450,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1751,39 +1502,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1804,39 +1555,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1856,39 +1607,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 20:32:33 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (DjHMcVqBnq)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1908,40 +1659,40 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:54:28 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 29.08 in an attempt to settle your Amazon.ca seller account balance.
@@ -1957,39 +1708,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 06:14:30 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (X8HTY1kPjb)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2015,39 +1766,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Feb 2026 17:52:28 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2068,39 +1819,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Feb 2026 21:45:54 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (SOu11lTFx5)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2126,39 +1877,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -2173,39 +1924,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2229,39 +1980,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2275,39 +2026,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2324,39 +2075,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2376,39 +2127,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 15:38:46 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2425,39 +2176,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 16:06:24 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2481,39 +2232,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 14:48:41 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2533,39 +2284,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 14:12:31 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2585,39 +2336,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Feb 2026 14:54:33 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -2633,39 +2384,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Feb 2026 13:38:32 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2685,39 +2436,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Feb 2026 13:37:02 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2737,39 +2488,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -2788,39 +2539,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2838,39 +2589,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2892,39 +2643,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2947,39 +2698,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2998,39 +2749,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3049,39 +2800,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3101,39 +2852,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3153,39 +2904,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 Actie vereist: Belangrijke informatie over je productvermeldingen
@@ -3203,39 +2954,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3253,39 +3004,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Rispondi ai requisiti di conformità per le tue offerte</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 Azione richiesta: Informazioni importanti sulle sue offerte
@@ -3303,39 +3054,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3354,39 +3105,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 05:28:30 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3404,40 +3155,40 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 08:54:27 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3455,39 +3206,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 05:31:26 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3505,39 +3256,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 21:23:05 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3555,39 +3306,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:18:58 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3602,39 +3353,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 09:56:14 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3650,39 +3401,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 05:24:39 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3700,39 +3451,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 21:13:50 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3750,39 +3501,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:49 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3800,40 +3551,40 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 11:03:26 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 26/04/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 26/04/2026 to avoid shipping restrictions
@@ -3852,39 +3603,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 05:20:21 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3902,39 +3653,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Feb 2026 16:07:02 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit Product Safety Law compliance information for Saudi Arabia</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  You can now submit PSL compliance information through the listing workflow and Manage All Inventory.
@@ -3956,39 +3707,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 20:18:57 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -4006,39 +3757,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:12:51 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4057,39 +3808,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:10:23 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4108,39 +3859,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 16:27:54 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Notificaciones automáticas de Amazon Seller Central (favor de no responder a este mensaje) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento para los listados</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 Acción requerida: Información importante sobre tus listados de productos
@@ -4157,39 +3908,185 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Hola, Weihai EU:
+ Para cumplir nuestros requisitos de registro del impuesto sobre el valor añadido (IVA) europeo, necesitamos que nos proporciones más información.
+ ¿A qué se debe esto?
+ De acuerdo con nuestros requisitos de registro a efectos fiscales en Europa, tienes que proporcionarnos un número de identificación fiscal válido de todos los países en los que consideremos que tienes obligación de registrarte a efectos fiscales o confirmar el estado de registro en la Ventanilla Única del IVA (OSS) en tu país de origen.
+ Hemos detectado que tu cuenta tiene que cumplir una serie de requisitos para el registro a efectos fiscales en la Unión Europea, el Reino Unido, Noruega y Suiza, donde tienes la obligación de registrarte a efectos fiscales. En concreto, es posible que tengas que tomar medidas para lo siguiente:
+ Polonia
+ Para más información, consulta Información sobre el impuesto sobre el valor añadido (IVA) europeo .
+ ¿Cómo evito la desactivación de mi cuenta?
+ Para evitar la desactivación de la cuenta, consulta la sección "Acciones prioritarias" de la página Estado de la cuenta en los próximos 45 días. Desde ahí podrás hacer lo siguiente:
+- Revisar la información que tienes </t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Dzień dobry Weihai EU,
+ potrzebujemy od Ciebie dodatkowych informacji, które pozwolą Ci spełnić europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT.
+ Dlaczego tak się stało?
+ Zgodnie z europejskimi wymaganiami Amazon dotyczącymi rejestracji jako podatnik VAT musisz podać nam ważny numer VAT dla wszystkich krajów, w których według nas podlegasz obowiązkowi rejestracji jako podatnik VAT, lub potwierdzenie statusu rejestracji w procedurze unijnej w Twoim kraju macierzystym.
+ Ustaliliśmy, że w przypadku Twojego konta w Unii Europejskiej, Zjednoczonym Królestwie, Norwegii i Szwajcarii, gdzie masz zobowiązania z tytułu VAT, istnieją wymogi w zakresie rejestracji jako podatnik VAT. Podjęcie działań może być w szczególności wymagane w następujących przypadkach:
+ Polska
+ Więcej informacji znajdziesz na stronie Informacje dotyczące podatku VAT w Europie .
+ Jak mogę zapobiec dezaktywacji konta?
+ Aby uniknąć dezaktywacji konta, w ciągu najbliższych 45 dni odwiedź sekcję „Działania priorytetowe” na stronie Kondycja konta . W sekcji tej można:
+- zweryfikować istniejące informacje dotyczące wymienionych krajów
+- przesłać informacje o VAT za pośrednictwem portali „Informacje o</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
+ la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Gentile Weihai EU,
+ Ai fini della conformità ai requisiti di registrazione IVA in Europa di Amazon, ti chiediamo di fornirci ulteriori informazioni.
+ Ciò a cosa è dovuto?
+ In base ai requisiti di registrazione IVA in Europa di Amazon, sei tenuto a fornirci un numero di partita IVA valido per tutti i paesi in cui riteniamo che tu abbia l'obbligo di effettuare tale registrazione o una conferma dello stato Union One-Stop Shop (OSS) relativo al tuo paese di registrazione.
+ Vi sono dei requisiti per la registrazione ai fini IVA che il tuo account deve soddisfare nei paesi in cui sei soggetto a obblighi in materia di IVA (stati dell'Unione europea, Regno Unito, Norvegia e Svizzera). Nello specifico, potrebbe essere necessario un intervento da parte tua per quanto segue:
+ Polonia
+ Per maggiori informazioni, consulta la pagina di aiuto Informazioni sull'IVA in Europa .
+ Come faccio a evitare la disattivazione dell'account?
+ Per evitare la disattivazione dell'account, visita entro i prossimi 45 giorni la sezione relativa alle azioni prioritarie della pagina Stato dell'account . Da qui, potrai effettuare le seguenti operazioni:
+- Verificare le informazioni esistenti per i paesi in elenco</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4209,39 +4106,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -4257,40 +4154,40 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4306,39 +4203,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4355,39 +4252,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4406,39 +4303,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4456,39 +4353,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -4500,39 +4397,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4544,39 +4441,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -4588,39 +4485,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4632,39 +4529,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4676,39 +4573,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -4720,39 +4617,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4764,39 +4661,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4808,39 +4705,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -4858,39 +4755,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -4933,39 +4830,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4982,40 +4879,40 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5033,39 +4930,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5083,39 +4980,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5127,39 +5024,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5171,39 +5068,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5222,39 +5119,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5266,39 +5163,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5310,39 +5207,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5354,39 +5251,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5398,39 +5295,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5442,39 +5339,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5486,39 +5383,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5530,39 +5427,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5574,39 +5471,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5618,40 +5515,40 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5670,39 +5567,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5714,40 +5611,40 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -5759,39 +5656,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5803,39 +5700,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5854,39 +5751,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5898,39 +5795,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5949,39 +5846,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -5993,39 +5890,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6041,40 +5938,40 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6092,39 +5989,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6142,39 +6039,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -6190,39 +6087,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -6240,39 +6137,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -6313,39 +6210,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6363,40 +6260,40 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6414,39 +6311,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6463,39 +6360,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6513,39 +6410,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 11:10:25 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6563,39 +6460,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 00:58:56 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>最后机会：请在3月9日前提报春季促销日的促销</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>3月9日前提报春季促销日促销
 尊敬的卖家，
@@ -6610,39 +6507,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 21:40:34 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6656,39 +6553,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 11:10:30 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6704,39 +6601,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:13:10 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 60 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -6752,39 +6649,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:09:55 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 60 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6801,40 +6698,40 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:07:47 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 60 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6850,39 +6747,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 18:30:15 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para marzo</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para marzo
@@ -6911,39 +6808,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:58 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6960,40 +6857,40 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:56 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7010,39 +6907,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:35 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7057,40 +6954,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:40 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7105,39 +7002,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:31 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7152,39 +7049,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:23 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7199,39 +7096,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 15:01:07 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7246,39 +7143,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 10:49:26 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -7306,39 +7203,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:09:03 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados
@@ -7352,39 +7249,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7407,39 +7304,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7461,39 +7358,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7516,39 +7413,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7571,39 +7468,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>New removal fees for KSA apply starting March 30</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
@@ -7629,39 +7526,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 13:57:30 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-12</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7683,39 +7580,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 12:08:33 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7739,39 +7636,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 13:32:21 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Stranded SKUs scheduled for automatic removal</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 Stranded SKUs scheduled for automatic removal
@@ -7783,39 +7680,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Feb 2026 13:43:58 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7839,39 +7736,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Feb 2026 13:32:50 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-05</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7889,6 +7786,109 @@
 - Check your complete list and quantity of unsellable items in the Manage FBA inventory .
 - Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
  To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>[Action Required] Provide additional information within 45 days to
+ avoid account deactivation under European VAT registration requirements</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai EU,
+ We need you to provide additional information in order to comply with Amazon’s European Value Added Tax (VAT) registration requirements.
+ Why is this happening?
+ According to Amazon’s European VAT registration requirements you must provide us with a valid VAT Registration Number (‘VRN’) for all the countries in which we believe you have a VAT registration obligation or confirmation of the Union One-Stop Shop (OSS) status for your home country.
+ We identified VAT registration requirements for your account in the European Union, the United Kingdom, Norway, and Switzerland in which you have VAT obligation. Specifically, action may be required for the following:
+ Poland
+ To learn more, go to the European Value Added Tax Information Help page.
+ How do I avoid account deactivation?
+ To avoid account deactivation, within the next 45 days visit the Priority Actions section on your Account Health page . From there, you will be able to:
+- Verify your existing information for listed countries
+- Submit VAT information through Business Information and Tax Setting portals
+- Submit required documentation for extension or exemption requests
+ What happens if I don’t provide th</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>[Action required] Provide additional information within 45 days to
+ avoid account deactivation under European VAT registration requirements</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai EU,
+ We need you to provide additional information in order to comply with Amazon’s European Value Added Tax (VAT) registration requirements.
+ Why is this happening?
+ According to Amazon’s European VAT registration requirements, you must provide us with a valid VAT registration number (“VRN”) for all the countries in which we believe you have a VAT registration obligation, or confirmation of the Union One-Stop Shop (OSS) status for your home country.
+ We identified VAT registration requirements for your account in the European Union, the United Kingdom, Norway and Switzerland in which you have Value Added Tax (VAT) obligation. Specifically, action may be required for the following:
+ Poland
+ To learn more, go to the European Value Added Tax information help page.
+ How do I avoid account deactivation?
+ To avoid account deactivation, within the next 45 days visit the Priority actions section on your Account Health page . From there, you will be able to:
+- Verify your existing information for listed countries
+- Submit Value Added Tax (VAT) information through business information and tax setting portals
+- Submit required documentation for extension or exemption request</t>
         </is>
       </c>
     </row>

--- a/important_mails_2026-03-22.xlsx
+++ b/important_mails_2026-03-22.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1095,7 +1095,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1110,68 +1110,21 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
+          <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Pagamento elaborato con successo</t>
+          <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
- Tentativo di pagamento
-Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
-In data 03/15/26 14:54 CET, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
- 200,42.
- Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
- Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
- Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che p</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-04-02</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1192,39 +1145,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1248,39 +1201,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1303,40 +1256,40 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -1352,39 +1305,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1404,39 +1357,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -1450,39 +1403,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1502,39 +1455,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1555,39 +1508,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1607,39 +1560,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 20:32:33 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (DjHMcVqBnq)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1659,40 +1612,40 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:54:28 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 29.08 in an attempt to settle your Amazon.ca seller account balance.
@@ -1708,39 +1661,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 06:14:30 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (X8HTY1kPjb)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1766,39 +1719,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Feb 2026 17:52:28 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1819,97 +1772,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 19 Feb 2026 21:45:54 +0000</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA removal request is complete (SOu11lTFx5)</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed and shipped your removal
-request (SOu11lTFx5) to the address you specified before.
-Return Summary:
-Quantity Requested: 2
-Quantity Successfully Shipped: 2
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being shipped, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-4303247-5655239
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-738874004554169</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -1924,39 +1819,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1980,39 +1875,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2026,39 +1921,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2075,39 +1970,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2127,39 +2022,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 15:38:46 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2176,39 +2071,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 16:06:24 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2232,39 +2127,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 14:48:41 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2284,39 +2179,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 14:12:31 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2336,39 +2231,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Feb 2026 14:54:33 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -2384,39 +2279,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Feb 2026 13:38:32 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2436,39 +2331,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Feb 2026 13:37:02 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2488,39 +2383,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -2539,39 +2434,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2589,39 +2484,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2643,39 +2538,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2698,39 +2593,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2749,39 +2644,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2800,39 +2695,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -2852,39 +2747,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -2904,39 +2799,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 Actie vereist: Belangrijke informatie over je productvermeldingen
@@ -2954,39 +2849,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3004,39 +2899,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Rispondi ai requisiti di conformità per le tue offerte</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 Azione richiesta: Informazioni importanti sulle sue offerte
@@ -3054,39 +2949,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3105,39 +3000,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 05:28:30 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3155,40 +3050,40 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 08:54:27 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3206,39 +3101,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 05:31:26 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3256,39 +3151,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 21:23:05 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3306,39 +3201,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:18:58 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3353,39 +3248,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 09:56:14 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3401,39 +3296,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 05:24:39 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3451,39 +3346,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 21:13:50 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3501,39 +3396,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:49 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3551,40 +3446,40 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 11:03:26 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 26/04/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 26/04/2026 to avoid shipping restrictions
@@ -3603,39 +3498,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 05:20:21 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3653,39 +3548,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Feb 2026 16:07:02 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Submit Product Safety Law compliance information for Saudi Arabia</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  You can now submit PSL compliance information through the listing workflow and Manage All Inventory.
@@ -3707,39 +3602,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 20:18:57 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3757,39 +3652,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:12:51 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -3808,39 +3703,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:10:23 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -3859,39 +3754,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 16:27:54 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Notificaciones automáticas de Amazon Seller Central (favor de no responder a este mensaje) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento para los listados</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 Acción requerida: Información importante sobre tus listados de productos
@@ -3908,39 +3803,86 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Pagamento elaborato con successo</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
+ Tentativo di pagamento
+Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
+In data 03/15/26 14:54 CET, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
+ 200,42.
+ Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
+ Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
+ Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che p</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -3956,39 +3898,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4005,40 +3947,40 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -4054,39 +3996,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4106,39 +4048,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -4154,40 +4096,40 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4203,39 +4145,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4252,39 +4194,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4303,39 +4245,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4353,39 +4295,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -4397,39 +4339,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4441,39 +4383,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -4485,39 +4427,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4529,39 +4471,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4573,39 +4515,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -4617,39 +4559,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4661,39 +4603,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4705,39 +4647,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -4755,39 +4697,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -4830,39 +4772,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4879,40 +4821,40 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -4930,39 +4872,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -4980,39 +4922,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5024,39 +4966,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5068,39 +5010,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5119,39 +5061,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5163,39 +5105,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5207,39 +5149,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5251,39 +5193,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5295,39 +5237,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5339,39 +5281,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5383,39 +5325,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5427,39 +5369,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5471,39 +5413,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5515,40 +5457,40 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5567,39 +5509,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5611,40 +5553,40 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -5656,39 +5598,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5700,39 +5642,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5751,39 +5693,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5795,39 +5737,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5846,39 +5788,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -5890,39 +5832,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -5938,40 +5880,40 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -5989,39 +5931,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6039,39 +5981,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -6087,39 +6029,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -6137,39 +6079,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -6210,39 +6152,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6260,40 +6202,40 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6311,39 +6253,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6360,39 +6302,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6410,39 +6352,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 11:10:25 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6460,39 +6402,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 00:58:56 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>最后机会：请在3月9日前提报春季促销日的促销</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>3月9日前提报春季促销日促销
 尊敬的卖家，
@@ -6507,39 +6449,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 21:40:34 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6553,39 +6495,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 11:10:30 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6601,39 +6543,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:13:10 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 60 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -6649,39 +6591,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:09:55 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 60 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6698,40 +6640,40 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:07:47 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 60 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6747,39 +6689,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 18:30:15 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para marzo</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para marzo
@@ -6808,39 +6750,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:58 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6857,40 +6799,40 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:56 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6907,39 +6849,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:35 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6954,40 +6896,40 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:40 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7002,39 +6944,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:31 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7049,39 +6991,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:23 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7096,39 +7038,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 15:01:07 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7143,39 +7085,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 10:49:26 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -7203,39 +7145,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:09:03 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados
@@ -7249,39 +7191,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7304,39 +7246,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7358,39 +7300,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7413,39 +7355,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7468,39 +7410,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>New removal fees for KSA apply starting March 30</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
@@ -7526,39 +7468,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 13:57:30 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-12</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7580,39 +7522,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 12:08:33 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7636,39 +7578,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 13:32:21 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Stranded SKUs scheduled for automatic removal</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 Stranded SKUs scheduled for automatic removal
@@ -7680,149 +7622,40 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 20 Feb 2026 13:43:58 +0000</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- DjHMcVqBnq
- Unsellable Products:
-- FNSKU: X0025OLRH7 Quantity: 1
-- FNSKU: X0025UXT4F Quantity: 1
-- FNSKU: X002A05YW5 Quantity: 1
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Centra</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 20 Feb 2026 13:32:50 +0000</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-03-05</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated removals of unfulfillable inventory
- Required removals: First notification
- Required removals: First notification
- Hello,
-Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-03-05 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
-Unsellable products:
-- FNSKU: X002C17O8J Quantity: 1
- Why is this happening?
-This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
-We leveraged a combination of automated means to identify this issue and make this decision.
- How do I address this?
-Follow these steps to manage your unsellable inventory:
-- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
-- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
- To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7841,40 +7674,40 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7892,39 +7725,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -7938,39 +7771,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -7988,39 +7821,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -8037,39 +7870,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -8087,40 +7920,40 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -8139,39 +7972,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres
@@ -8187,39 +8020,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Sun, 1 Mar 2026 00:16:30 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>View your US Q1-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q1-2026
@@ -8249,40 +8082,40 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:10:48 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8301,40 +8134,40 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:06:07 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8352,39 +8185,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 01:35:07 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Upload proof of insurance and explore new best practices guide</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
  Upload proof of commercial liability insurance by March 30, 2026. Review our new best practices guide for mainland China-based sellers to help you avoid common coverage gaps and policy issues.
